--- a/artfynd/A 26681-2025 artfynd.xlsx
+++ b/artfynd/A 26681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56124540</v>
+        <v>110886964</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grekland, Upl</t>
+          <t>Västanån, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630756.9635120168</v>
+        <v>630746</v>
       </c>
       <c r="R2" t="n">
-        <v>6721670.935284689</v>
+        <v>6721695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110886964</v>
+        <v>110886965</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630746</v>
+        <v>630795</v>
       </c>
       <c r="R3" t="n">
-        <v>6721695</v>
+        <v>6721685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110886978</v>
+        <v>110886979</v>
       </c>
       <c r="B4" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630818</v>
+        <v>630768</v>
       </c>
       <c r="R4" t="n">
-        <v>6721620</v>
+        <v>6721585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På äldre igenväxt skogsbilväg (troligen från avverkning)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110886987</v>
+        <v>110886984</v>
       </c>
       <c r="B5" t="n">
-        <v>103146</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630711</v>
+        <v>630766</v>
       </c>
       <c r="R5" t="n">
-        <v>6721529</v>
+        <v>6721578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110886979</v>
+        <v>110886967</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630768</v>
+        <v>630821</v>
       </c>
       <c r="R6" t="n">
-        <v>6721585</v>
+        <v>6721663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110886981</v>
+        <v>110886978</v>
       </c>
       <c r="B7" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630841</v>
+        <v>630818</v>
       </c>
       <c r="R7" t="n">
-        <v>6721604</v>
+        <v>6721620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På äldre igenväxt skogsbilväg (troligen från avverkning)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110886986</v>
+        <v>110886980</v>
       </c>
       <c r="B8" t="n">
-        <v>103146</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630748</v>
+        <v>630716</v>
       </c>
       <c r="R8" t="n">
-        <v>6721541</v>
+        <v>6721535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110886983</v>
+        <v>56124540</v>
       </c>
       <c r="B9" t="n">
-        <v>97672</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,17 +1387,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västanån, Upl</t>
+          <t>Grekland, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630772</v>
+        <v>630757</v>
       </c>
       <c r="R9" t="n">
-        <v>6721586</v>
+        <v>6721671</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,12 +1433,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2014-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2014-06-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,27 +1453,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110886982</v>
+        <v>110886971</v>
       </c>
       <c r="B10" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630823</v>
+        <v>630885</v>
       </c>
       <c r="R10" t="n">
-        <v>6721594</v>
+        <v>6721701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,15 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110886984</v>
+        <v>110886983</v>
       </c>
       <c r="B11" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630766</v>
+        <v>630772</v>
       </c>
       <c r="R11" t="n">
-        <v>6721578</v>
+        <v>6721586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,37 +1659,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110886980</v>
+        <v>110886966</v>
       </c>
       <c r="B12" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630716</v>
+        <v>630848</v>
       </c>
       <c r="R12" t="n">
-        <v>6721535</v>
+        <v>6721687</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,32 +1756,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110886985</v>
+        <v>110886981</v>
       </c>
       <c r="B13" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1861,10 +1791,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630764</v>
+        <v>630841</v>
       </c>
       <c r="R13" t="n">
-        <v>6721575</v>
+        <v>6721604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,15 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110886965</v>
+        <v>110886982</v>
       </c>
       <c r="B14" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1864,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630795</v>
+        <v>630823</v>
       </c>
       <c r="R14" t="n">
-        <v>6721685</v>
+        <v>6721594</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,32 +1950,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110886966</v>
+        <v>110886985</v>
       </c>
       <c r="B15" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2065,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630848</v>
+        <v>630764</v>
       </c>
       <c r="R15" t="n">
-        <v>6721687</v>
+        <v>6721575</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,15 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110886967</v>
+        <v>110886991</v>
       </c>
       <c r="B16" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,21 +2058,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630821</v>
+        <v>630680</v>
       </c>
       <c r="R16" t="n">
-        <v>6721663</v>
+        <v>6721553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,6 +2141,297 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110886963</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630702</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6721645</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110886986</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630748</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6721541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110886987</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630711</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6721529</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26681-2025 artfynd.xlsx
+++ b/artfynd/A 26681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886980</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124540</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886971</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886966</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886981</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886982</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886985</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886991</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886986</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,8 +2522,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886987</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>